--- a/Middlesbrough vs York 10112024.xlsx
+++ b/Middlesbrough vs York 10112024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cex\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cex\Desktop\Rugby Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614BEAC2-EFA0-48EE-B91F-144D7334194C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B610BEB-F458-41F8-98C8-A4DB62C6866E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{B269B7FD-F2CF-4041-B0A7-A1CBE45257CE}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" firstSheet="1" activeTab="3" xr2:uid="{B269B7FD-F2CF-4041-B0A7-A1CBE45257CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Midlesbrough 22-entries" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="56">
   <si>
     <t>Complete Pass</t>
   </si>
@@ -191,7 +191,22 @@
     <t>AXAAAA</t>
   </si>
   <si>
-    <t>22 Entries</t>
+    <t>22 Entries For</t>
+  </si>
+  <si>
+    <t>22 Entries Against</t>
+  </si>
+  <si>
+    <t>Game Time</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1331,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1393,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1870,10 +1885,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13612793-D2A0-4007-9A5D-3ACA5CA9B547}">
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1893,7 +1908,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -1934,8 +1949,11 @@
       <c r="T1" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U1" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>40</v>
       </c>
@@ -1955,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -1994,10 +2012,13 @@
         <v>22</v>
       </c>
       <c r="T2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+      <c r="U2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>6</v>
       </c>
@@ -2017,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -2056,10 +2077,13 @@
         <v>5</v>
       </c>
       <c r="T3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>11</v>
       </c>
@@ -2079,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -2118,10 +2142,13 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>22</v>
       </c>
@@ -2141,7 +2168,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -2180,10 +2207,13 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2</v>
       </c>
@@ -2203,7 +2233,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -2242,10 +2272,13 @@
         <v>2</v>
       </c>
       <c r="T6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>7</v>
       </c>
@@ -2265,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -2304,10 +2337,13 @@
         <v>3</v>
       </c>
       <c r="T7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>9</v>
       </c>
@@ -2327,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2366,6 +2402,9 @@
         <v>3</v>
       </c>
       <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
         <v>0</v>
       </c>
     </row>
@@ -2376,10 +2415,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25878DB5-7998-4162-BB81-B491E9AA45D2}">
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2399,7 +2438,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -2440,8 +2479,14 @@
       <c r="T1" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>45</v>
       </c>
@@ -2461,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -2500,10 +2545,16 @@
         <v>26</v>
       </c>
       <c r="T2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="U2">
+        <v>3</v>
+      </c>
+      <c r="W2">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3</v>
       </c>
@@ -2517,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2550,7 +2601,7 @@
         <v>35</v>
       </c>
       <c r="R3">
-        <v>1817</v>
+        <v>485</v>
       </c>
       <c r="S3">
         <v>3</v>
@@ -2558,8 +2609,14 @@
       <c r="T3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>6</v>
       </c>
@@ -2576,7 +2633,7 @@
         <v>6</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -2609,16 +2666,22 @@
         <v>36</v>
       </c>
       <c r="R4">
+        <v>833</v>
+      </c>
+      <c r="S4">
+        <v>2</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="W4">
         <v>2650</v>
       </c>
-      <c r="S4">
-        <v>2</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>31</v>
       </c>
@@ -2635,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -2668,16 +2731,22 @@
         <v>47</v>
       </c>
       <c r="R5">
-        <v>3560</v>
+        <v>910</v>
       </c>
       <c r="S5">
         <v>7</v>
       </c>
       <c r="T5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>10</v>
       </c>
@@ -2694,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -2727,16 +2796,22 @@
         <v>49</v>
       </c>
       <c r="R6">
-        <v>3921</v>
+        <v>361</v>
       </c>
       <c r="S6">
         <v>7</v>
       </c>
       <c r="T6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2753,7 +2828,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -2786,16 +2861,22 @@
         <v>48</v>
       </c>
       <c r="R7">
-        <v>4168</v>
+        <v>247</v>
       </c>
       <c r="S7">
         <v>7</v>
       </c>
       <c r="T7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2812,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2845,13 +2926,19 @@
         <v>26</v>
       </c>
       <c r="R8">
-        <v>4714</v>
+        <v>546</v>
       </c>
       <c r="S8">
         <v>4</v>
       </c>
       <c r="T8">
         <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>4714</v>
       </c>
     </row>
   </sheetData>
